--- a/Data/weapons_melee_table.xlsx
+++ b/Data/weapons_melee_table.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Stat_blocks\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88742770-D462-43DC-8C11-00A7F8126442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80D5B75-398B-4DFB-8E63-273429307715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41580" yWindow="2865" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="-1"/>
+    <workbookView xWindow="3075" yWindow="1620" windowWidth="32175" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="General" sheetId="1" r:id="rId4"/>
+    <sheet name="General" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="118">
   <si>
     <t>Name</t>
   </si>
@@ -323,14 +323,64 @@
   </si>
   <si>
     <t>D6 7 —</t>
+  </si>
+  <si>
+    <t>Tentacle* 40% 2D6</t>
+  </si>
+  <si>
+    <t>Walktapus</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Constrict</t>
+  </si>
+  <si>
+    <t>Auto 1 —</t>
+  </si>
+  <si>
+    <t>Gas Cloud</t>
+  </si>
+  <si>
+    <t>The gas cloud is systemic with a POT equal to the walktapus’ CON. All within its 3-meter radius must try to hold their breath (as per asphyxiation rules). If the gas is inhaled, the gas is immediately harmful—if the victim’s CON is overcome, they take damage equal to the gas’ full potency. If they resist, they still take damage equal to half the potency of the gas. Each round that more gas is inhaled, the victim must attempt to resist again.</t>
+  </si>
+  <si>
+    <t>Auto Poison,</t>
+  </si>
+  <si>
+    <t>POT=CON</t>
+  </si>
+  <si>
+    <t>1D4-1</t>
+  </si>
+  <si>
+    <t>Ham Beetle</t>
+  </si>
+  <si>
+    <t>If the damage for its bite attack is reduced to 0, or less, consider the result as 0.</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>Giant Honeybee Drone</t>
+  </si>
+  <si>
+    <t>A bee can both bite and sting in the same melee round. The sting injects poison with a POT equal to one half the bee’s CON score. It can also impale (see description above).</t>
+  </si>
+  <si>
+    <t>D4 7 -</t>
+  </si>
+  <si>
+    <t>Giant Honeybee Worker</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -364,8 +414,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -669,23 +719,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.796293258666992" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.33203125" customWidth="1"/>
-    <col min="3" max="3" width="12.826241493225098" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.620946884155273" customWidth="1"/>
-    <col min="7" max="7" width="14.28674602508545" customWidth="1"/>
-    <col min="8" max="8" width="238.189697265625" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="5" width="9.33203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="403.6640625" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" customWidth="1"/>
-    <col min="10" max="10" width="20.392431259155273" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,954 +766,1138 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="0">
-        <v>10</v>
-      </c>
-      <c r="C2" s="0" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>6</v>
       </c>
-      <c r="E2" s="0">
+      <c r="E2">
         <v>4</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="0">
-        <v>10</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>8</v>
       </c>
-      <c r="E3" s="0">
+      <c r="E3">
         <v>3</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>8</v>
       </c>
-      <c r="E4" s="0">
+      <c r="E4">
         <v>3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="0">
-        <v>10</v>
-      </c>
-      <c r="E5" s="0">
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="0">
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="0">
-        <v>10</v>
-      </c>
-      <c r="E6" s="0">
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="0">
+      <c r="B7">
         <v>15</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="0">
+      <c r="E7">
         <v>4</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="0">
+      <c r="B8">
         <v>15</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>8</v>
       </c>
-      <c r="E8" s="0">
+      <c r="E8">
         <v>4</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="0">
+      <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>6</v>
       </c>
-      <c r="E9" s="0">
+      <c r="E9">
         <v>4</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="0">
+      <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>6</v>
       </c>
-      <c r="E10" s="0">
+      <c r="E10">
         <v>3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="0">
-        <v>10</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>12</v>
       </c>
-      <c r="E11" s="0">
+      <c r="E11">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="0">
-        <v>10</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>12</v>
       </c>
-      <c r="E12" s="0">
+      <c r="E12">
         <v>2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="0">
-        <v>10</v>
-      </c>
-      <c r="C13" s="0" t="s">
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>8</v>
       </c>
-      <c r="E13" s="0">
+      <c r="E13">
         <v>2</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="0">
-        <v>10</v>
-      </c>
-      <c r="C14" s="0" t="s">
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>12</v>
       </c>
-      <c r="E14" s="0">
+      <c r="E14">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="0">
+      <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>12</v>
       </c>
-      <c r="E15" s="0">
+      <c r="E15">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="0">
+      <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="0">
-        <v>10</v>
-      </c>
-      <c r="E16" s="0">
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16">
         <v>2</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="0">
+      <c r="B17">
         <v>5</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>12</v>
       </c>
-      <c r="E17" s="0">
+      <c r="E17">
         <v>2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="0">
+      <c r="B18">
         <v>25</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>8</v>
       </c>
-      <c r="E18" s="0">
+      <c r="E18">
         <v>4</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="0">
+      <c r="B19">
         <v>25</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>4</v>
       </c>
-      <c r="E19" s="0">
+      <c r="E19">
         <v>4</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="0">
+      <c r="B20">
         <v>25</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="0">
+      <c r="E20">
         <v>4</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="0">
+      <c r="B21">
         <v>25</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>42</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="0">
+      <c r="E21">
         <v>4</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="0">
+      <c r="B22">
         <v>25</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" t="s">
         <v>44</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="0">
+      <c r="E22">
         <v>4</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="0">
+      <c r="B23">
         <v>15</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="0">
+      <c r="E23">
         <v>4</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="0">
+      <c r="B24">
         <v>50</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="0">
+      <c r="E24">
         <v>4</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="0">
-        <v>10</v>
-      </c>
-      <c r="C25" s="0" t="s">
+      <c r="B25">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="0">
+      <c r="D25">
         <v>8</v>
       </c>
-      <c r="E25" s="0">
+      <c r="E25">
         <v>2</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="0">
+      <c r="B26">
         <v>5</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="0">
-        <v>10</v>
-      </c>
-      <c r="E26" s="0">
+      <c r="D26">
+        <v>10</v>
+      </c>
+      <c r="E26">
         <v>2</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="0">
+      <c r="B27">
         <v>5</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="0">
-        <v>10</v>
-      </c>
-      <c r="E27" s="0">
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27">
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="0">
+      <c r="B28">
         <v>15</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="0">
+      <c r="D28">
         <v>12</v>
       </c>
-      <c r="E28" s="0">
+      <c r="E28">
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="0">
+      <c r="B29">
         <v>15</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" t="s">
         <v>33</v>
       </c>
-      <c r="D29" s="0">
-        <v>10</v>
-      </c>
-      <c r="E29" s="0">
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29">
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="0">
+      <c r="B30">
         <v>15</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" t="s">
         <v>25</v>
       </c>
-      <c r="D30" s="0">
-        <v>10</v>
-      </c>
-      <c r="E30" s="0">
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30">
         <v>1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>57</v>
       </c>
-      <c r="B31" s="0">
-        <v>10</v>
-      </c>
-      <c r="C31" s="0" t="s">
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="0">
-        <v>10</v>
-      </c>
-      <c r="E31" s="0">
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31">
         <v>3</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="0">
+      <c r="B32">
         <v>5</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="0">
+      <c r="D32">
         <v>5</v>
       </c>
-      <c r="E32" s="0">
+      <c r="E32">
         <v>1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="0">
-        <v>10</v>
-      </c>
-      <c r="C33" s="0" t="s">
+      <c r="B33">
+        <v>10</v>
+      </c>
+      <c r="C33" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="0">
+      <c r="D33">
         <v>12</v>
       </c>
-      <c r="E33" s="0">
+      <c r="E33">
         <v>1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="0">
+      <c r="B34">
         <v>15</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="0">
-        <v>10</v>
-      </c>
-      <c r="E34" s="0">
+      <c r="D34">
+        <v>10</v>
+      </c>
+      <c r="E34">
         <v>3</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="0">
+      <c r="B35">
         <v>15</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" t="s">
         <v>58</v>
       </c>
-      <c r="D35" s="0">
+      <c r="D35">
         <v>6</v>
       </c>
-      <c r="E35" s="0">
+      <c r="E35">
         <v>3</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="0">
+      <c r="B36">
         <v>15</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="0">
+      <c r="D36">
         <v>5</v>
       </c>
-      <c r="E36" s="0">
+      <c r="E36">
         <v>4</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="0">
+      <c r="B37">
         <v>15</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="0">
-        <v>10</v>
-      </c>
-      <c r="E37" s="0">
+      <c r="D37">
+        <v>10</v>
+      </c>
+      <c r="E37">
         <v>4</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="0">
+      <c r="B38">
         <v>55</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="0">
-        <v>10</v>
-      </c>
-      <c r="E38" s="0">
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38">
         <v>3</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="0">
-        <v>10</v>
-      </c>
-      <c r="C39" s="0" t="s">
+      <c r="B39">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
         <v>13</v>
       </c>
-      <c r="D39" s="0">
-        <v>10</v>
-      </c>
-      <c r="E39" s="0">
+      <c r="D39">
+        <v>10</v>
+      </c>
+      <c r="E39">
         <v>3</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="0">
+      <c r="B40">
         <v>15</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" t="s">
         <v>69</v>
       </c>
-      <c r="D40" s="0">
+      <c r="D40">
         <v>8</v>
       </c>
-      <c r="E40" s="0">
+      <c r="E40">
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="0">
+      <c r="B41">
         <v>40</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" t="s">
         <v>46</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="D41" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="0">
+      <c r="E41">
         <v>4</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="0">
+      <c r="B42">
         <v>55</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" t="s">
         <v>46</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" t="s">
         <v>72</v>
       </c>
-      <c r="E42" s="0">
+      <c r="E42">
         <v>4</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="0">
+      <c r="B43">
         <v>40</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="0">
+      <c r="E43">
         <v>4</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="F43" t="s">
         <v>73</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="G43" t="s">
         <v>70</v>
       </c>
-      <c r="H43" s="0" t="s">
+      <c r="H43" t="s">
         <v>74</v>
       </c>
-      <c r="J43" s="0" t="s">
+      <c r="J43" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="0">
+      <c r="B44">
         <v>30</v>
       </c>
-      <c r="C44" s="0" t="s">
+      <c r="C44" t="s">
         <v>46</v>
       </c>
-      <c r="E44" s="0">
+      <c r="E44">
         <v>8</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" t="s">
         <v>76</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="G44" t="s">
         <v>38</v>
       </c>
-      <c r="H44" s="0" t="s">
+      <c r="H44" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>78</v>
       </c>
-      <c r="B45" s="0">
+      <c r="B45">
         <v>75</v>
       </c>
-      <c r="C45" s="0" t="s">
+      <c r="C45" t="s">
         <v>79</v>
       </c>
-      <c r="E45" s="0">
+      <c r="E45">
         <v>2</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="F45" t="s">
         <v>76</v>
       </c>
-      <c r="G45" s="0" t="s">
+      <c r="G45" t="s">
         <v>78</v>
       </c>
-      <c r="H45" s="0" t="s">
+      <c r="H45" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>81</v>
       </c>
-      <c r="B46" s="0">
+      <c r="B46">
         <v>90</v>
       </c>
-      <c r="E46" s="0">
+      <c r="E46">
         <v>9</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="F46" t="s">
         <v>82</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="G46" t="s">
         <v>81</v>
       </c>
-      <c r="H46" s="0" t="s">
+      <c r="H46" t="s">
         <v>83</v>
       </c>
-      <c r="J46" s="0" t="s">
+      <c r="J46" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>70</v>
       </c>
-      <c r="B47" s="0">
+      <c r="B47">
         <v>90</v>
       </c>
-      <c r="C47" s="0" t="s">
+      <c r="C47" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="0">
+      <c r="E47">
         <v>9</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="F47" t="s">
         <v>82</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="G47" t="s">
         <v>70</v>
       </c>
-      <c r="H47" s="0" t="s">
+      <c r="H47" t="s">
         <v>84</v>
       </c>
-      <c r="J47" s="0" t="s">
+      <c r="J47" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>86</v>
       </c>
-      <c r="B48" s="0">
+      <c r="B48">
         <v>0</v>
       </c>
-      <c r="E48" s="0">
+      <c r="E48">
         <v>0</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="F48" t="s">
         <v>82</v>
       </c>
-      <c r="J48" s="0" t="s">
+      <c r="J48" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>88</v>
       </c>
-      <c r="B49" s="0">
+      <c r="B49">
         <v>50</v>
       </c>
-      <c r="C49" s="0" t="s">
+      <c r="C49" t="s">
         <v>89</v>
       </c>
-      <c r="E49" s="0">
+      <c r="E49">
         <v>7</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="F49" t="s">
         <v>90</v>
       </c>
-      <c r="G49" s="0" t="s">
+      <c r="G49" t="s">
         <v>88</v>
       </c>
-      <c r="H49" s="0" t="s">
+      <c r="H49" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>92</v>
       </c>
-      <c r="B50" s="0">
+      <c r="B50">
         <v>50</v>
       </c>
-      <c r="C50" s="0" t="s">
+      <c r="C50" t="s">
         <v>46</v>
       </c>
-      <c r="E50" s="0">
+      <c r="E50">
         <v>6</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="F50" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
         <v>93</v>
       </c>
-      <c r="B51" s="0">
+      <c r="B51">
         <v>75</v>
       </c>
-      <c r="E51" s="0">
+      <c r="E51">
         <v>6</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="F51" t="s">
         <v>90</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="G51" t="s">
         <v>93</v>
       </c>
-      <c r="H51" s="0" t="s">
+      <c r="H51" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="0">
+      <c r="B52">
         <v>40</v>
       </c>
-      <c r="C52" s="0" t="s">
+      <c r="C52" t="s">
         <v>95</v>
       </c>
-      <c r="E52" s="0">
+      <c r="E52">
         <v>12</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="F52" t="s">
         <v>96</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="G52" t="s">
         <v>64</v>
       </c>
-      <c r="H52" s="0" t="s">
+      <c r="H52" t="s">
         <v>97</v>
       </c>
-      <c r="J52" s="0" t="s">
+      <c r="J52" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="0">
+      <c r="B53">
         <v>50</v>
       </c>
-      <c r="C53" s="0" t="s">
+      <c r="C53" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="0">
+      <c r="E53">
         <v>0</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="F53" t="s">
         <v>96</v>
       </c>
-      <c r="G53" s="0" t="s">
+      <c r="G53" t="s">
         <v>38</v>
       </c>
-      <c r="H53" s="0" t="s">
+      <c r="H53" t="s">
         <v>99</v>
       </c>
-      <c r="J53" s="0" t="s">
+      <c r="J53" t="s">
         <v>100</v>
       </c>
     </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>102</v>
+      </c>
+      <c r="J54" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55" t="s">
+        <v>89</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55" t="s">
+        <v>102</v>
+      </c>
+      <c r="J55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>102</v>
+      </c>
+      <c r="G56" t="s">
+        <v>106</v>
+      </c>
+      <c r="H56" t="s">
+        <v>107</v>
+      </c>
+      <c r="J56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57" t="s">
+        <v>102</v>
+      </c>
+      <c r="J57" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>110</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>111</v>
+      </c>
+      <c r="G58" t="s">
+        <v>70</v>
+      </c>
+      <c r="H58" t="s">
+        <v>112</v>
+      </c>
+      <c r="J58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59">
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59" t="s">
+        <v>117</v>
+      </c>
+      <c r="G59" t="s">
+        <v>70</v>
+      </c>
+      <c r="H59" t="s">
+        <v>115</v>
+      </c>
+      <c r="J59" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60">
+        <v>30</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60" t="s">
+        <v>117</v>
+      </c>
+      <c r="G60" t="s">
+        <v>71</v>
+      </c>
+      <c r="H60" t="s">
+        <v>115</v>
+      </c>
+      <c r="J60" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61">
+        <v>30</v>
+      </c>
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>114</v>
+      </c>
+      <c r="G61" t="s">
+        <v>70</v>
+      </c>
+      <c r="H61" t="s">
+        <v>115</v>
+      </c>
+      <c r="J61" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/weapons_melee_table.xlsx
+++ b/Data/weapons_melee_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Stat_blocks\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80D5B75-398B-4DFB-8E63-273429307715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7563EC1D-6DEC-46CF-AC8B-1A2C1BA8D0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="1620" windowWidth="32175" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="2340" windowWidth="32175" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="119">
   <si>
     <t>Name</t>
   </si>
@@ -364,16 +364,19 @@
     <t>D4</t>
   </si>
   <si>
+    <t>Giant Honeybee Worker</t>
+  </si>
+  <si>
+    <t>A bee can both bite and sting in the same melee round. The sting injects poison with a POT equal to one half the bee’s CON score. It can also impale (see description above).</t>
+  </si>
+  <si>
+    <t>D4 7 -</t>
+  </si>
+  <si>
     <t>Giant Honeybee Drone</t>
   </si>
   <si>
-    <t>A bee can both bite and sting in the same melee round. The sting injects poison with a POT equal to one half the bee’s CON score. It can also impale (see description above).</t>
-  </si>
-  <si>
-    <t>D4 7 -</t>
-  </si>
-  <si>
-    <t>Giant Honeybee Worker</t>
+    <t>Giant Honeybee Queen</t>
   </si>
 </sst>
 </file>
@@ -720,14 +723,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.33203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" customWidth="1"/>
     <col min="8" max="8" width="403.6640625" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" customWidth="1"/>
@@ -1833,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G59" t="s">
         <v>70</v>
@@ -1859,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G60" t="s">
         <v>71</v>
@@ -1885,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G61" t="s">
         <v>70</v>
@@ -1894,6 +1897,58 @@
         <v>115</v>
       </c>
       <c r="J61" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62">
+        <v>80</v>
+      </c>
+      <c r="C62" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="s">
+        <v>118</v>
+      </c>
+      <c r="G62" t="s">
+        <v>70</v>
+      </c>
+      <c r="H62" t="s">
+        <v>115</v>
+      </c>
+      <c r="J62" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63">
+        <v>80</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63" t="s">
+        <v>118</v>
+      </c>
+      <c r="G63" t="s">
+        <v>71</v>
+      </c>
+      <c r="H63" t="s">
+        <v>115</v>
+      </c>
+      <c r="J63" t="s">
         <v>116</v>
       </c>
     </row>

--- a/Data/weapons_melee_table.xlsx
+++ b/Data/weapons_melee_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\Stat_blocks\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7563EC1D-6DEC-46CF-AC8B-1A2C1BA8D0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDE12E8-BCCA-4B87-B1B2-0B45EA46B4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="2340" windowWidth="32175" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="1620" windowWidth="32175" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="General" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="119">
   <si>
     <t>Name</t>
   </si>
@@ -349,9 +349,6 @@
     <t>Auto Poison,</t>
   </si>
   <si>
-    <t>POT=CON</t>
-  </si>
-  <si>
     <t>1D4-1</t>
   </si>
   <si>
@@ -377,6 +374,9 @@
   </si>
   <si>
     <t>Giant Honeybee Queen</t>
+  </si>
+  <si>
+    <t>Auto</t>
   </si>
 </sst>
 </file>
@@ -723,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" customWidth="1"/>
@@ -1721,7 +1721,7 @@
         <v>101</v>
       </c>
       <c r="B54">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C54" t="s">
         <v>89</v>
@@ -1740,8 +1740,8 @@
       <c r="A55" t="s">
         <v>104</v>
       </c>
-      <c r="B55">
-        <v>0</v>
+      <c r="B55" t="s">
+        <v>118</v>
       </c>
       <c r="C55" t="s">
         <v>89</v>
@@ -1760,8 +1760,8 @@
       <c r="A56" t="s">
         <v>106</v>
       </c>
-      <c r="B56">
-        <v>0</v>
+      <c r="B56" t="s">
+        <v>118</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -1781,19 +1781,28 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
         <v>109</v>
       </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
       <c r="E57">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>102</v>
+        <v>110</v>
+      </c>
+      <c r="G57" t="s">
+        <v>70</v>
+      </c>
+      <c r="H57" t="s">
+        <v>111</v>
       </c>
       <c r="J57" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
@@ -1801,30 +1810,30 @@
         <v>70</v>
       </c>
       <c r="B58">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C58" t="s">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="E58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G58" t="s">
         <v>70</v>
       </c>
       <c r="H58" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J58" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B59">
         <v>30</v>
@@ -1836,21 +1845,21 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
+        <v>113</v>
+      </c>
+      <c r="G59" t="s">
+        <v>71</v>
+      </c>
+      <c r="H59" t="s">
         <v>114</v>
       </c>
-      <c r="G59" t="s">
-        <v>70</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="J59" t="s">
         <v>115</v>
-      </c>
-      <c r="J59" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B60">
         <v>30</v>
@@ -1862,16 +1871,16 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
+        <v>116</v>
+      </c>
+      <c r="G60" t="s">
+        <v>70</v>
+      </c>
+      <c r="H60" t="s">
         <v>114</v>
       </c>
-      <c r="G60" t="s">
-        <v>71</v>
-      </c>
-      <c r="H60" t="s">
+      <c r="J60" t="s">
         <v>115</v>
-      </c>
-      <c r="J60" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
@@ -1879,7 +1888,7 @@
         <v>70</v>
       </c>
       <c r="B61">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="C61" t="s">
         <v>11</v>
@@ -1894,15 +1903,15 @@
         <v>70</v>
       </c>
       <c r="H61" t="s">
+        <v>114</v>
+      </c>
+      <c r="J61" t="s">
         <v>115</v>
-      </c>
-      <c r="J61" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B62">
         <v>80</v>
@@ -1914,42 +1923,16 @@
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H62" t="s">
+        <v>114</v>
+      </c>
+      <c r="J62" t="s">
         <v>115</v>
-      </c>
-      <c r="J62" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63">
-        <v>80</v>
-      </c>
-      <c r="C63" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63" t="s">
-        <v>118</v>
-      </c>
-      <c r="G63" t="s">
-        <v>71</v>
-      </c>
-      <c r="H63" t="s">
-        <v>115</v>
-      </c>
-      <c r="J63" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>
